--- a/bin/Debug/Logs/202507/Log_20250723-170926.xlsx
+++ b/bin/Debug/Logs/202507/Log_20250723-170926.xlsx
@@ -409,6 +409,108 @@
   </x:si>
   <x:si>
     <x:t>[error][2025-07-24 22:05:09]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-25 16:17:19]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-25 16:24:48]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>@START_INFO ZRS202506200955_TE_LIN:DESKTOP-M5HPH95:HM:RS70B64G4M08G:E9002B:AE35:FT3_RS70B64G4M08G_032003007_032003003::320:::FT::R80544:FT3:FT:25+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>@INFO_OK+</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-25 16:30:46]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-25 16:34:02]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-25 20:17:22]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-25 20:19:28]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-25 20:19:33]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-25 20:20:19]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-25 20:25:01]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-25 20:25:44]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-26 08:35:42]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-26 08:42:53]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-26 08:44:11]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-26 08:55:09]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-26 15:10:00]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-26 15:23:40]：InitCard() System.Exception: 执行指令:  GT_Open
 打开控制器失败(-6)
    在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
    在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
@@ -4010,6 +4112,706 @@
         <x:v>11</x:v>
       </x:c>
     </x:row>
+    <x:row r="232" spans="1:4">
+      <x:c r="A232" s="1">
+        <x:v>45863.6787030208</x:v>
+      </x:c>
+      <x:c r="B232" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C232" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D232" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="233" spans="1:4">
+      <x:c r="A233" s="1">
+        <x:v>45863.6787033681</x:v>
+      </x:c>
+      <x:c r="B233" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C233" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D233" s="2" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="234" spans="1:4">
+      <x:c r="A234" s="1">
+        <x:v>45863.6788386227</x:v>
+      </x:c>
+      <x:c r="B234" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C234" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D234" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="235" spans="1:4">
+      <x:c r="A235" s="1">
+        <x:v>45863.6838957639</x:v>
+      </x:c>
+      <x:c r="B235" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C235" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D235" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="236" spans="1:4">
+      <x:c r="A236" s="1">
+        <x:v>45863.6838962384</x:v>
+      </x:c>
+      <x:c r="B236" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C236" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D236" s="2" t="s">
+        <x:v>102</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="237" spans="1:4">
+      <x:c r="A237" s="1">
+        <x:v>45863.6840304745</x:v>
+      </x:c>
+      <x:c r="B237" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C237" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D237" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="238" spans="1:4">
+      <x:c r="A238" s="1">
+        <x:v>45863.6840482639</x:v>
+      </x:c>
+      <x:c r="B238" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C238" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D238" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="239" spans="1:4">
+      <x:c r="A239" s="1">
+        <x:v>45863.6840496759</x:v>
+      </x:c>
+      <x:c r="B239" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C239" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D239" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="240" spans="1:4">
+      <x:c r="A240" s="1">
+        <x:v>45863.6880433333</x:v>
+      </x:c>
+      <x:c r="B240" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C240" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D240" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="241" spans="1:4">
+      <x:c r="A241" s="1">
+        <x:v>45863.6880434954</x:v>
+      </x:c>
+      <x:c r="B241" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C241" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D241" s="2" t="s">
+        <x:v>105</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="242" spans="1:4">
+      <x:c r="A242" s="1">
+        <x:v>45863.6903121644</x:v>
+      </x:c>
+      <x:c r="B242" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C242" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D242" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="243" spans="1:4">
+      <x:c r="A243" s="1">
+        <x:v>45863.6903123611</x:v>
+      </x:c>
+      <x:c r="B243" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C243" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D243" s="2" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="244" spans="1:4">
+      <x:c r="A244" s="1">
+        <x:v>45863.6904448495</x:v>
+      </x:c>
+      <x:c r="B244" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C244" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D244" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="245" spans="1:4">
+      <x:c r="A245" s="1">
+        <x:v>45863.8454046296</x:v>
+      </x:c>
+      <x:c r="B245" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C245" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D245" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="246" spans="1:4">
+      <x:c r="A246" s="1">
+        <x:v>45863.8454047801</x:v>
+      </x:c>
+      <x:c r="B246" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C246" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D246" s="2" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="247" spans="1:4">
+      <x:c r="A247" s="1">
+        <x:v>45863.8455334375</x:v>
+      </x:c>
+      <x:c r="B247" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C247" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D247" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="248" spans="1:4">
+      <x:c r="A248" s="1">
+        <x:v>45863.8468530903</x:v>
+      </x:c>
+      <x:c r="B248" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C248" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D248" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="249" spans="1:4">
+      <x:c r="A249" s="1">
+        <x:v>45863.846853125</x:v>
+      </x:c>
+      <x:c r="B249" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C249" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D249" s="2" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="250" spans="1:4">
+      <x:c r="A250" s="1">
+        <x:v>45863.8469117824</x:v>
+      </x:c>
+      <x:c r="B250" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C250" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D250" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="251" spans="1:4">
+      <x:c r="A251" s="1">
+        <x:v>45863.8469118171</x:v>
+      </x:c>
+      <x:c r="B251" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C251" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D251" s="2" t="s">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="252" spans="1:4">
+      <x:c r="A252" s="1">
+        <x:v>45863.8469821412</x:v>
+      </x:c>
+      <x:c r="B252" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C252" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D252" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="253" spans="1:4">
+      <x:c r="A253" s="1">
+        <x:v>45863.8474442361</x:v>
+      </x:c>
+      <x:c r="B253" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C253" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D253" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="254" spans="1:4">
+      <x:c r="A254" s="1">
+        <x:v>45863.8474442708</x:v>
+      </x:c>
+      <x:c r="B254" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C254" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D254" s="2" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="255" spans="1:4">
+      <x:c r="A255" s="1">
+        <x:v>45863.8475718287</x:v>
+      </x:c>
+      <x:c r="B255" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C255" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D255" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="256" spans="1:4">
+      <x:c r="A256" s="1">
+        <x:v>45863.8507067245</x:v>
+      </x:c>
+      <x:c r="B256" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C256" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D256" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="257" spans="1:4">
+      <x:c r="A257" s="1">
+        <x:v>45863.850706875</x:v>
+      </x:c>
+      <x:c r="B257" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C257" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D257" s="2" t="s">
+        <x:v>111</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="258" spans="1:4">
+      <x:c r="A258" s="1">
+        <x:v>45863.8508362269</x:v>
+      </x:c>
+      <x:c r="B258" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C258" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D258" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="259" spans="1:4">
+      <x:c r="A259" s="1">
+        <x:v>45863.8512059954</x:v>
+      </x:c>
+      <x:c r="B259" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C259" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D259" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="260" spans="1:4">
+      <x:c r="A260" s="1">
+        <x:v>45863.8512060301</x:v>
+      </x:c>
+      <x:c r="B260" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C260" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D260" s="2" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="261" spans="1:4">
+      <x:c r="A261" s="1">
+        <x:v>45863.8513351389</x:v>
+      </x:c>
+      <x:c r="B261" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C261" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D261" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="262" spans="1:4">
+      <x:c r="A262" s="1">
+        <x:v>45864.3581277199</x:v>
+      </x:c>
+      <x:c r="B262" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C262" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D262" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="263" spans="1:4">
+      <x:c r="A263" s="1">
+        <x:v>45864.3581279167</x:v>
+      </x:c>
+      <x:c r="B263" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C263" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D263" s="2" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="264" spans="1:4">
+      <x:c r="A264" s="1">
+        <x:v>45864.3582581597</x:v>
+      </x:c>
+      <x:c r="B264" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C264" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D264" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="265" spans="1:4">
+      <x:c r="A265" s="1">
+        <x:v>45864.3631155208</x:v>
+      </x:c>
+      <x:c r="B265" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C265" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D265" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266" spans="1:4">
+      <x:c r="A266" s="1">
+        <x:v>45864.363115706</x:v>
+      </x:c>
+      <x:c r="B266" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C266" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D266" s="2" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267" spans="1:4">
+      <x:c r="A267" s="1">
+        <x:v>45864.3632450926</x:v>
+      </x:c>
+      <x:c r="B267" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C267" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D267" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="268" spans="1:4">
+      <x:c r="A268" s="1">
+        <x:v>45864.3633014583</x:v>
+      </x:c>
+      <x:c r="B268" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C268" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D268" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="269" spans="1:4">
+      <x:c r="A269" s="1">
+        <x:v>45864.3640186111</x:v>
+      </x:c>
+      <x:c r="B269" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C269" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D269" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="270" spans="1:4">
+      <x:c r="A270" s="1">
+        <x:v>45864.3640188426</x:v>
+      </x:c>
+      <x:c r="B270" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C270" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D270" s="2" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="271" spans="1:4">
+      <x:c r="A271" s="1">
+        <x:v>45864.3641511343</x:v>
+      </x:c>
+      <x:c r="B271" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C271" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D271" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="272" spans="1:4">
+      <x:c r="A272" s="1">
+        <x:v>45864.3681305324</x:v>
+      </x:c>
+      <x:c r="B272" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C272" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D272" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="273" spans="1:4">
+      <x:c r="A273" s="1">
+        <x:v>45864.3716367824</x:v>
+      </x:c>
+      <x:c r="B273" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C273" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D273" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="274" spans="1:4">
+      <x:c r="A274" s="1">
+        <x:v>45864.3716369444</x:v>
+      </x:c>
+      <x:c r="B274" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C274" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D274" s="2" t="s">
+        <x:v>116</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="275" spans="1:4">
+      <x:c r="A275" s="1">
+        <x:v>45864.3717704861</x:v>
+      </x:c>
+      <x:c r="B275" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C275" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D275" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="276" spans="1:4">
+      <x:c r="A276" s="1">
+        <x:v>45864.6319513194</x:v>
+      </x:c>
+      <x:c r="B276" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C276" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D276" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="277" spans="1:4">
+      <x:c r="A277" s="1">
+        <x:v>45864.6319514815</x:v>
+      </x:c>
+      <x:c r="B277" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C277" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D277" s="2" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="278" spans="1:4">
+      <x:c r="A278" s="1">
+        <x:v>45864.6320845139</x:v>
+      </x:c>
+      <x:c r="B278" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C278" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D278" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="279" spans="1:4">
+      <x:c r="A279" s="1">
+        <x:v>45864.6414440856</x:v>
+      </x:c>
+      <x:c r="B279" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C279" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D279" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="280" spans="1:4">
+      <x:c r="A280" s="1">
+        <x:v>45864.6414442361</x:v>
+      </x:c>
+      <x:c r="B280" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C280" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D280" s="2" t="s">
+        <x:v>118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="281" spans="1:4">
+      <x:c r="A281" s="1">
+        <x:v>45864.6415760648</x:v>
+      </x:c>
+      <x:c r="B281" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C281" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D281" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/bin/Debug/Logs/202507/Log_20250723-170926.xlsx
+++ b/bin/Debug/Logs/202507/Log_20250723-170926.xlsx
@@ -514,6 +514,153 @@
 打开控制器失败(-6)
    在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
    在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 11:29:46]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 11:31:15]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIN_A区Tray侧定位气缸原位输出失败！未初始化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIN_A区Tray侧定位气缸到位输出失败！未初始化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 11:32:46]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIN_B区Tray侧定位气缸原位输出失败！未初始化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BIN_B区Tray侧定位气缸到位输出失败！未初始化</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 12:00:19]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 17:29:23]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[Auto侧敲使能]:False-&gt;True:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[前侧同时敲击]:False-&gt;True:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[放料时允许侧敲]:True-&gt;False:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[侧敲时允许放料]:True-&gt;False:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[放置多少颗敲击]:8-&gt;9:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[Auto侧敲次数]:2-&gt;3:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[侧敲间隔]:100-&gt;101:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[Auto侧敲使能]:True-&gt;False:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[前侧同时敲击]:True-&gt;False:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[放置多少颗敲击]:9-&gt;8:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[Auto侧敲次数]:3-&gt;2:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[侧敲间隔]:101-&gt;100:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[放料时允许侧敲]:False-&gt;True:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>档案名称:[8X19_UFS_OnLine]:测试机名称:[8X19_UFS_OnLine]:[侧敲时允许放料]:False-&gt;True:更新成功</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 19:58:39]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>命令：select * from f_ZRS240929001A_20250606_22_18_02  order by 获取MAP时间，错误信息：对象名 'f_ZRS240929001A_20250606_22_18_02' 无效。</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 20:24:53]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 20:31:09]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 20:54:43]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 20:57:07]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 21:00:37]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 21:05:09]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 21:20:35]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 45
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-28 22:06:37]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
+  </x:si>
+  <x:si>
+    <x:t>[error][2025-07-29 09:38:21]：InitCard() System.Exception: 执行指令:  GT_Open
+打开控制器失败(-6)
+   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
+   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -4812,6 +4959,1098 @@
         <x:v>11</x:v>
       </x:c>
     </x:row>
+    <x:row r="282" spans="1:4">
+      <x:c r="A282" s="1">
+        <x:v>45866.4790051968</x:v>
+      </x:c>
+      <x:c r="B282" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C282" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D282" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="283" spans="1:4">
+      <x:c r="A283" s="1">
+        <x:v>45866.4790055556</x:v>
+      </x:c>
+      <x:c r="B283" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C283" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D283" s="2" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="284" spans="1:4">
+      <x:c r="A284" s="1">
+        <x:v>45866.479136794</x:v>
+      </x:c>
+      <x:c r="B284" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C284" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D284" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="285" spans="1:4">
+      <x:c r="A285" s="1">
+        <x:v>45866.4800403704</x:v>
+      </x:c>
+      <x:c r="B285" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C285" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D285" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="286" spans="1:4">
+      <x:c r="A286" s="1">
+        <x:v>45866.4800405671</x:v>
+      </x:c>
+      <x:c r="B286" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C286" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D286" s="2" t="s">
+        <x:v>120</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="287" spans="1:4">
+      <x:c r="A287" s="1">
+        <x:v>45866.4801778125</x:v>
+      </x:c>
+      <x:c r="B287" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C287" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D287" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="288" spans="1:4">
+      <x:c r="A288" s="1">
+        <x:v>45866.4803325347</x:v>
+      </x:c>
+      <x:c r="B288" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C288" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D288" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="289" spans="1:4">
+      <x:c r="A289" s="1">
+        <x:v>45866.4803337153</x:v>
+      </x:c>
+      <x:c r="B289" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C289" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D289" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="290" spans="1:4">
+      <x:c r="A290" s="1">
+        <x:v>45866.480335</x:v>
+      </x:c>
+      <x:c r="B290" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C290" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D290" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="291" spans="1:4">
+      <x:c r="A291" s="1">
+        <x:v>45866.4810938426</x:v>
+      </x:c>
+      <x:c r="B291" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C291" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D291" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="292" spans="1:4">
+      <x:c r="A292" s="1">
+        <x:v>45866.4810940162</x:v>
+      </x:c>
+      <x:c r="B292" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C292" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D292" s="2" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="293" spans="1:4">
+      <x:c r="A293" s="1">
+        <x:v>45866.4812266551</x:v>
+      </x:c>
+      <x:c r="B293" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C293" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D293" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="294" spans="1:4">
+      <x:c r="A294" s="1">
+        <x:v>45866.4812873264</x:v>
+      </x:c>
+      <x:c r="B294" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C294" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D294" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="295" spans="1:4">
+      <x:c r="A295" s="1">
+        <x:v>45866.4812885995</x:v>
+      </x:c>
+      <x:c r="B295" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C295" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D295" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="296" spans="1:4">
+      <x:c r="A296" s="1">
+        <x:v>45866.4812898727</x:v>
+      </x:c>
+      <x:c r="B296" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C296" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D296" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="297" spans="1:4">
+      <x:c r="A297" s="1">
+        <x:v>45866.4812911458</x:v>
+      </x:c>
+      <x:c r="B297" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C297" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D297" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="298" spans="1:4">
+      <x:c r="A298" s="1">
+        <x:v>45866.4813013079</x:v>
+      </x:c>
+      <x:c r="B298" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C298" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D298" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="299" spans="1:4">
+      <x:c r="A299" s="1">
+        <x:v>45866.4813026389</x:v>
+      </x:c>
+      <x:c r="B299" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C299" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D299" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="300" spans="1:4">
+      <x:c r="A300" s="1">
+        <x:v>45866.4813039468</x:v>
+      </x:c>
+      <x:c r="B300" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C300" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D300" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="301" spans="1:4">
+      <x:c r="A301" s="1">
+        <x:v>45866.4813051736</x:v>
+      </x:c>
+      <x:c r="B301" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C301" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D301" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="302" spans="1:4">
+      <x:c r="A302" s="1">
+        <x:v>45866.4838017708</x:v>
+      </x:c>
+      <x:c r="B302" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C302" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D302" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="303" spans="1:4">
+      <x:c r="A303" s="1">
+        <x:v>45866.483803125</x:v>
+      </x:c>
+      <x:c r="B303" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C303" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D303" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="304" spans="1:4">
+      <x:c r="A304" s="1">
+        <x:v>45866.4838043982</x:v>
+      </x:c>
+      <x:c r="B304" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C304" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D304" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="305" spans="1:4">
+      <x:c r="A305" s="1">
+        <x:v>45866.4838056713</x:v>
+      </x:c>
+      <x:c r="B305" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C305" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D305" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="306" spans="1:4">
+      <x:c r="A306" s="1">
+        <x:v>45866.483812419</x:v>
+      </x:c>
+      <x:c r="B306" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C306" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D306" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="307" spans="1:4">
+      <x:c r="A307" s="1">
+        <x:v>45866.4838136921</x:v>
+      </x:c>
+      <x:c r="B307" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C307" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D307" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="308" spans="1:4">
+      <x:c r="A308" s="1">
+        <x:v>45866.4838149653</x:v>
+      </x:c>
+      <x:c r="B308" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C308" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D308" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="309" spans="1:4">
+      <x:c r="A309" s="1">
+        <x:v>45866.4838162384</x:v>
+      </x:c>
+      <x:c r="B309" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C309" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D309" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="310" spans="1:4">
+      <x:c r="A310" s="1">
+        <x:v>45866.5002221991</x:v>
+      </x:c>
+      <x:c r="B310" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C310" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D310" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="311" spans="1:4">
+      <x:c r="A311" s="1">
+        <x:v>45866.5002223843</x:v>
+      </x:c>
+      <x:c r="B311" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C311" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D311" s="2" t="s">
+        <x:v>126</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="312" spans="1:4">
+      <x:c r="A312" s="1">
+        <x:v>45866.5003612963</x:v>
+      </x:c>
+      <x:c r="B312" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C312" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D312" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="313" spans="1:4">
+      <x:c r="A313" s="1">
+        <x:v>45866.7287473958</x:v>
+      </x:c>
+      <x:c r="B313" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C313" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D313" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="314" spans="1:4">
+      <x:c r="A314" s="1">
+        <x:v>45866.7287479514</x:v>
+      </x:c>
+      <x:c r="B314" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C314" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D314" s="2" t="s">
+        <x:v>127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="315" spans="1:4">
+      <x:c r="A315" s="1">
+        <x:v>45866.7288914815</x:v>
+      </x:c>
+      <x:c r="B315" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C315" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D315" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="316" spans="1:4">
+      <x:c r="A316" s="1">
+        <x:v>45866.7292688542</x:v>
+      </x:c>
+      <x:c r="B316" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C316" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D316" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="317" spans="1:4">
+      <x:c r="A317" s="1">
+        <x:v>45866.7295477778</x:v>
+      </x:c>
+      <x:c r="B317" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C317" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D317" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="318" spans="1:4">
+      <x:c r="A318" s="1">
+        <x:v>45866.7297837963</x:v>
+      </x:c>
+      <x:c r="B318" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C318" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D318" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="319" spans="1:4">
+      <x:c r="A319" s="1">
+        <x:v>45866.7297838079</x:v>
+      </x:c>
+      <x:c r="B319" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C319" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D319" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="320" spans="1:4">
+      <x:c r="A320" s="1">
+        <x:v>45866.7300675926</x:v>
+      </x:c>
+      <x:c r="B320" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C320" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D320" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="321" spans="1:4">
+      <x:c r="A321" s="1">
+        <x:v>45866.7300676042</x:v>
+      </x:c>
+      <x:c r="B321" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C321" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D321" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="322" spans="1:4">
+      <x:c r="A322" s="1">
+        <x:v>45866.7300676157</x:v>
+      </x:c>
+      <x:c r="B322" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C322" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D322" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="323" spans="1:4">
+      <x:c r="A323" s="1">
+        <x:v>45866.7303671875</x:v>
+      </x:c>
+      <x:c r="B323" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C323" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D323" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="324" spans="1:4">
+      <x:c r="A324" s="1">
+        <x:v>45866.7303671991</x:v>
+      </x:c>
+      <x:c r="B324" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C324" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D324" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="325" spans="1:4">
+      <x:c r="A325" s="1">
+        <x:v>45866.7303671991</x:v>
+      </x:c>
+      <x:c r="B325" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C325" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D325" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="326" spans="1:4">
+      <x:c r="A326" s="1">
+        <x:v>45866.7303672107</x:v>
+      </x:c>
+      <x:c r="B326" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C326" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D326" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="327" spans="1:4">
+      <x:c r="A327" s="1">
+        <x:v>45866.7303672222</x:v>
+      </x:c>
+      <x:c r="B327" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C327" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D327" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="328" spans="1:4">
+      <x:c r="A328" s="1">
+        <x:v>45866.7303672222</x:v>
+      </x:c>
+      <x:c r="B328" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C328" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D328" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="329" spans="1:4">
+      <x:c r="A329" s="1">
+        <x:v>45866.7303672338</x:v>
+      </x:c>
+      <x:c r="B329" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C329" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D329" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="330" spans="1:4">
+      <x:c r="A330" s="1">
+        <x:v>45866.8324030208</x:v>
+      </x:c>
+      <x:c r="B330" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C330" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D330" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="331" spans="1:4">
+      <x:c r="A331" s="1">
+        <x:v>45866.832403206</x:v>
+      </x:c>
+      <x:c r="B331" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C331" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D331" s="2" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="332" spans="1:4">
+      <x:c r="A332" s="1">
+        <x:v>45866.8324728935</x:v>
+      </x:c>
+      <x:c r="B332" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C332" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D332" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="333" spans="1:4">
+      <x:c r="A333" s="1">
+        <x:v>45866.8325394907</x:v>
+      </x:c>
+      <x:c r="B333" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C333" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D333" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="334" spans="1:4">
+      <x:c r="A334" s="1">
+        <x:v>45866.8339431944</x:v>
+      </x:c>
+      <x:c r="B334" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C334" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D334" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="335" spans="1:4">
+      <x:c r="A335" s="1">
+        <x:v>45866.8506187037</x:v>
+      </x:c>
+      <x:c r="B335" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C335" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D335" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="336" spans="1:4">
+      <x:c r="A336" s="1">
+        <x:v>45866.8506190162</x:v>
+      </x:c>
+      <x:c r="B336" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C336" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D336" s="2" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="337" spans="1:4">
+      <x:c r="A337" s="1">
+        <x:v>45866.8507436458</x:v>
+      </x:c>
+      <x:c r="B337" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C337" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D337" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="338" spans="1:4">
+      <x:c r="A338" s="1">
+        <x:v>45866.8549716088</x:v>
+      </x:c>
+      <x:c r="B338" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C338" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D338" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="339" spans="1:4">
+      <x:c r="A339" s="1">
+        <x:v>45866.8549719213</x:v>
+      </x:c>
+      <x:c r="B339" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C339" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D339" s="2" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="340" spans="1:4">
+      <x:c r="A340" s="1">
+        <x:v>45866.8713402894</x:v>
+      </x:c>
+      <x:c r="B340" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C340" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D340" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="341" spans="1:4">
+      <x:c r="A341" s="1">
+        <x:v>45866.8713405903</x:v>
+      </x:c>
+      <x:c r="B341" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C341" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D341" s="2" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="342" spans="1:4">
+      <x:c r="A342" s="1">
+        <x:v>45866.8714680556</x:v>
+      </x:c>
+      <x:c r="B342" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C342" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D342" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="343" spans="1:4">
+      <x:c r="A343" s="1">
+        <x:v>45866.8730038889</x:v>
+      </x:c>
+      <x:c r="B343" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C343" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D343" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="344" spans="1:4">
+      <x:c r="A344" s="1">
+        <x:v>45866.8730040509</x:v>
+      </x:c>
+      <x:c r="B344" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C344" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D344" s="2" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="345" spans="1:4">
+      <x:c r="A345" s="1">
+        <x:v>45866.8731317245</x:v>
+      </x:c>
+      <x:c r="B345" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C345" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D345" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="346" spans="1:4">
+      <x:c r="A346" s="1">
+        <x:v>45866.8754299421</x:v>
+      </x:c>
+      <x:c r="B346" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C346" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D346" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="347" spans="1:4">
+      <x:c r="A347" s="1">
+        <x:v>45866.8754301157</x:v>
+      </x:c>
+      <x:c r="B347" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C347" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D347" s="2" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="348" spans="1:4">
+      <x:c r="A348" s="1">
+        <x:v>45866.8755558796</x:v>
+      </x:c>
+      <x:c r="B348" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C348" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D348" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="349" spans="1:4">
+      <x:c r="A349" s="1">
+        <x:v>45866.8785797917</x:v>
+      </x:c>
+      <x:c r="B349" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C349" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D349" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="350" spans="1:4">
+      <x:c r="A350" s="1">
+        <x:v>45866.8785799537</x:v>
+      </x:c>
+      <x:c r="B350" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C350" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D350" s="2" t="s">
+        <x:v>149</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="351" spans="1:4">
+      <x:c r="A351" s="1">
+        <x:v>45866.8787063194</x:v>
+      </x:c>
+      <x:c r="B351" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C351" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D351" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="352" spans="1:4">
+      <x:c r="A352" s="1">
+        <x:v>45866.8893041898</x:v>
+      </x:c>
+      <x:c r="B352" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C352" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D352" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="353" spans="1:4">
+      <x:c r="A353" s="1">
+        <x:v>45866.8893043982</x:v>
+      </x:c>
+      <x:c r="B353" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C353" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D353" s="2" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="354" spans="1:4">
+      <x:c r="A354" s="1">
+        <x:v>45866.8894530787</x:v>
+      </x:c>
+      <x:c r="B354" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C354" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D354" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="355" spans="1:4">
+      <x:c r="A355" s="1">
+        <x:v>45866.9212681019</x:v>
+      </x:c>
+      <x:c r="B355" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C355" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D355" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="356" spans="1:4">
+      <x:c r="A356" s="1">
+        <x:v>45866.9212682639</x:v>
+      </x:c>
+      <x:c r="B356" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C356" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D356" s="2" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="357" spans="1:4">
+      <x:c r="A357" s="1">
+        <x:v>45867.4016367708</x:v>
+      </x:c>
+      <x:c r="B357" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C357" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D357" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="358" spans="1:4">
+      <x:c r="A358" s="1">
+        <x:v>45867.401636956</x:v>
+      </x:c>
+      <x:c r="B358" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C358" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D358" s="2" t="s">
+        <x:v>152</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="359" spans="1:4">
+      <x:c r="A359" s="1">
+        <x:v>45867.4017601852</x:v>
+      </x:c>
+      <x:c r="B359" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C359" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D359" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
